--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-researchstudy.xlsx
@@ -454,7 +454,7 @@
     <t>ResearchStudy.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -492,7 +492,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -550,7 +550,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -690,7 +690,7 @@
     <t>ResearchStudy.protocol</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(PlanDefinition)
+    <t xml:space="preserve">Reference(PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -716,7 +716,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ResearchStudy)
+    <t xml:space="preserve">Reference(ResearchStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -778,7 +778,7 @@
     <t>研究の主な意図をコードします。 / Codes for the main intent of the study.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.primaryPurposeTypeCode</t>
@@ -799,7 +799,7 @@
     <t>臨床試験におけるヒトの初期実験的使用から市場後の評価への治療の進行の段階のコード。 / Codes for the stage in the progression of a therapy from initial experimental use in humans in clinical trials to post-market evaluation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-phase</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-phase|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.phaseCode</t>
@@ -859,7 +859,7 @@
     <t>状態または診断の識別。 / Identification of the condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>StudyCondition.code</t>
@@ -936,7 +936,7 @@
     <t>このアーティファクトが使用することを目的としている国と地域。 / Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.participatingLocationCode</t>
@@ -968,7 +968,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Group)
+    <t xml:space="preserve">Reference(Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1025,7 +1025,7 @@
     <t>ResearchStudy.sponsor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1050,7 +1050,7 @@
     <t>ResearchStudy.principalInvestigator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1069,7 +1069,7 @@
     <t>ResearchStudy.site</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1100,7 +1100,7 @@
     <t>研究が時期尚早に終了した理由をコードします。 / Codes for why the study ended prematurely.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped|4.0.1</t>
   </si>
   <si>
     <t>StudyOverallStatus.studyStoppedReasonCode</t>
@@ -1273,7 +1273,7 @@
     <t>学習目標の種類をコードします。 / Codes for the kind of study objective.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type|4.0.1</t>
   </si>
   <si>
     <t>StudyObjective.typeCode</t>
@@ -1606,7 +1606,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="32.32421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="41.3828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1621,7 +1621,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="147.1015625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.12890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.65625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
